--- a/apps/web/public/templates/08_المنصرف_من_المخازن.xlsx
+++ b/apps/web/public/templates/08_المنصرف_من_المخازن.xlsx
@@ -229,21 +229,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>المنظومة</author>
-  </authors>
-  <commentList>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>لو الشركة رجّعت جزء للمخازن</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1549,7 +1534,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1559,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1652,6 +1636,23 @@
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>شرح الأعمدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>• [المنصرف] كمية مرتجعة: لو الشركة رجّعت جزء للمخازن</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,6 +1694,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"المنصرف": [["232/2025/1/36", "PO25", "1.1.7", "6", "", "إذن 4512", ""]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/apps/web/public/templates/08_المنصرف_من_المخازن.xlsx
+++ b/apps/web/public/templates/08_المنصرف_من_المخازن.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>كمية مرتجعة</t>
+          <t>الكمية المُعادة للمخازن</t>
         </is>
       </c>
     </row>
@@ -1523,13 +1523,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="لازم تاريخ (يوم/شهر/سنة)" type="date" operator="greaterThan">
+    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="يجب إدخال تاريخ بصيغة يوم/شهر/سنة" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="G3:G5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1552,21 +1552,21 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>قالب المنصرف من المخازن</t>
+          <t>نموذج المنصرف من المخازن</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>الغرض: تسجيل المهمات المصروفة لكل أمر تكليف — بتتقارن بالمخطط والمنفذ والمفوتر.</t>
+          <t>الغرض: تسجيل المهمات المنصرفة لكل أمر تكليف — وتُقارن بالكميات المخططة والمنفذة والمفوترة.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>مين بيرفعه: المخازن والمشتريات.</t>
+          <t>الجهة المسؤولة عن الرفع: المخازن والمشتريات.</t>
         </is>
       </c>
     </row>
@@ -1576,14 +1576,14 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>• كل إذن صرف في صف. المرتجع بيتسجل في نفس الصف أو صف جديد بكمية مرتجعة.</t>
+          <t>• يُسجَّل كل إذن صرف في صف مستقل، وتُسجَّل الكمية المُعادة للمخازن في الصف نفسه أو في صف جديد.</t>
         </is>
       </c>
     </row>
@@ -1593,49 +1593,49 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>
@@ -1645,14 +1645,14 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>شرح الأعمدة</t>
+          <t>إيضاح الأعمدة</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>• [المنصرف] كمية مرتجعة: لو الشركة رجّعت جزء للمخازن</t>
+          <t>• [المنصرف] الكمية المُعادة للمخازن: في حال إعادة المقاول جزءاً من المهمات إلى المخازن</t>
         </is>
       </c>
     </row>
